--- a/grupos/3AEM - Estadisticos 20231.xlsx
+++ b/grupos/3AEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="138">
   <si>
     <t>Materia</t>
   </si>
@@ -3215,13 +3215,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:S33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="50.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16">
+    <row r="1" spans="1:19">
       <c r="A1" s="1"/>
       <c r="B1" s="1" t="s">
         <v>42</v>
@@ -3230,22 +3230,25 @@
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
       <c r="F1" s="1"/>
-      <c r="G1" s="1" t="s">
+      <c r="G1" s="1"/>
+      <c r="H1" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
       <c r="K1" s="1"/>
-      <c r="L1" s="1" t="s">
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16">
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3259,48 +3262,57 @@
         <v>7</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>9</v>
-      </c>
       <c r="K2" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="N2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="O2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="O2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16">
+      <c r="Q2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19">
       <c r="A3" s="1" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16">
+    <row r="4" spans="1:19">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3314,7 +3326,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -3332,7 +3344,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3349,8 +3361,17 @@
       <c r="P4">
         <v>100</v>
       </c>
-    </row>
-    <row r="5" spans="1:16">
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>100</v>
+      </c>
+      <c r="S4">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
@@ -3364,7 +3385,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -3382,7 +3403,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -3399,8 +3420,17 @@
       <c r="P5">
         <v>100</v>
       </c>
-    </row>
-    <row r="6" spans="1:16">
+      <c r="Q5">
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <v>100</v>
+      </c>
+      <c r="S5">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="A6" s="1" t="s">
         <v>14</v>
       </c>
@@ -3414,7 +3444,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3432,7 +3462,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3449,8 +3479,17 @@
       <c r="P6">
         <v>100</v>
       </c>
-    </row>
-    <row r="7" spans="1:16">
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>100</v>
+      </c>
+      <c r="S6">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
@@ -3464,7 +3503,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3482,7 +3521,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3499,8 +3538,17 @@
       <c r="P7">
         <v>100</v>
       </c>
-    </row>
-    <row r="8" spans="1:16">
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>100</v>
+      </c>
+      <c r="S7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="A8" s="1" t="s">
         <v>16</v>
       </c>
@@ -3514,7 +3562,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -3532,7 +3580,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3549,8 +3597,17 @@
       <c r="P8">
         <v>100</v>
       </c>
-    </row>
-    <row r="9" spans="1:16">
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>100</v>
+      </c>
+      <c r="S8">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="A9" s="1" t="s">
         <v>17</v>
       </c>
@@ -3564,7 +3621,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -3573,34 +3630,43 @@
         <v>100</v>
       </c>
       <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9">
         <v>90</v>
       </c>
-      <c r="I9">
-        <v>100</v>
-      </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L9">
         <v>100</v>
       </c>
       <c r="M9">
+        <v>100</v>
+      </c>
+      <c r="N9">
+        <v>100</v>
+      </c>
+      <c r="O9">
         <v>90</v>
       </c>
-      <c r="N9">
-        <v>100</v>
-      </c>
-      <c r="O9">
-        <v>100</v>
-      </c>
       <c r="P9">
         <v>100</v>
       </c>
-    </row>
-    <row r="10" spans="1:16">
+      <c r="Q9">
+        <v>0</v>
+      </c>
+      <c r="R9">
+        <v>100</v>
+      </c>
+      <c r="S9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
@@ -3614,7 +3680,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3632,7 +3698,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3649,8 +3715,17 @@
       <c r="P10">
         <v>100</v>
       </c>
-    </row>
-    <row r="11" spans="1:16">
+      <c r="Q10">
+        <v>0</v>
+      </c>
+      <c r="R10">
+        <v>100</v>
+      </c>
+      <c r="S10">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
@@ -3664,7 +3739,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3682,7 +3757,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3699,8 +3774,17 @@
       <c r="P11">
         <v>100</v>
       </c>
-    </row>
-    <row r="12" spans="1:16">
+      <c r="Q11">
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <v>100</v>
+      </c>
+      <c r="S11">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="A12" s="1" t="s">
         <v>20</v>
       </c>
@@ -3714,7 +3798,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -3732,7 +3816,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -3749,8 +3833,17 @@
       <c r="P12">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
+      <c r="Q12">
+        <v>0</v>
+      </c>
+      <c r="R12">
+        <v>100</v>
+      </c>
+      <c r="S12">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="A13" s="1" t="s">
         <v>21</v>
       </c>
@@ -3764,7 +3857,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -3773,34 +3866,43 @@
         <v>100</v>
       </c>
       <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13">
         <v>95</v>
       </c>
-      <c r="I13">
-        <v>100</v>
-      </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L13">
         <v>100</v>
       </c>
       <c r="M13">
+        <v>100</v>
+      </c>
+      <c r="N13">
+        <v>100</v>
+      </c>
+      <c r="O13">
         <v>95</v>
       </c>
-      <c r="N13">
-        <v>100</v>
-      </c>
-      <c r="O13">
-        <v>100</v>
-      </c>
       <c r="P13">
         <v>100</v>
       </c>
-    </row>
-    <row r="14" spans="1:16">
+      <c r="Q13">
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <v>100</v>
+      </c>
+      <c r="S13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="A14" s="1" t="s">
         <v>22</v>
       </c>
@@ -3814,7 +3916,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -3832,7 +3934,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -3849,8 +3951,17 @@
       <c r="P14">
         <v>100</v>
       </c>
-    </row>
-    <row r="15" spans="1:16">
+      <c r="Q14">
+        <v>0</v>
+      </c>
+      <c r="R14">
+        <v>100</v>
+      </c>
+      <c r="S14">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="A15" s="1" t="s">
         <v>23</v>
       </c>
@@ -3864,7 +3975,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -3882,7 +3993,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -3899,8 +4010,17 @@
       <c r="P15">
         <v>100</v>
       </c>
-    </row>
-    <row r="16" spans="1:16">
+      <c r="Q15">
+        <v>0</v>
+      </c>
+      <c r="R15">
+        <v>100</v>
+      </c>
+      <c r="S15">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="A16" s="1" t="s">
         <v>24</v>
       </c>
@@ -3914,7 +4034,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -3932,7 +4052,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -3949,8 +4069,17 @@
       <c r="P16">
         <v>100</v>
       </c>
-    </row>
-    <row r="17" spans="1:16">
+      <c r="Q16">
+        <v>0</v>
+      </c>
+      <c r="R16">
+        <v>100</v>
+      </c>
+      <c r="S16">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19">
       <c r="A17" s="1" t="s">
         <v>25</v>
       </c>
@@ -3964,7 +4093,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -3982,7 +4111,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -3999,8 +4128,17 @@
       <c r="P17">
         <v>100</v>
       </c>
-    </row>
-    <row r="18" spans="1:16">
+      <c r="Q17">
+        <v>0</v>
+      </c>
+      <c r="R17">
+        <v>100</v>
+      </c>
+      <c r="S17">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19">
       <c r="A18" s="1" t="s">
         <v>26</v>
       </c>
@@ -4014,14 +4152,14 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F18">
+        <v>100</v>
+      </c>
+      <c r="G18">
         <v>80</v>
       </c>
-      <c r="G18">
-        <v>100</v>
-      </c>
       <c r="H18">
         <v>100</v>
       </c>
@@ -4032,14 +4170,14 @@
         <v>100</v>
       </c>
       <c r="K18">
+        <v>0</v>
+      </c>
+      <c r="L18">
+        <v>100</v>
+      </c>
+      <c r="M18">
         <v>80</v>
       </c>
-      <c r="L18">
-        <v>100</v>
-      </c>
-      <c r="M18">
-        <v>100</v>
-      </c>
       <c r="N18">
         <v>100</v>
       </c>
@@ -4047,10 +4185,19 @@
         <v>100</v>
       </c>
       <c r="P18">
+        <v>100</v>
+      </c>
+      <c r="Q18">
+        <v>0</v>
+      </c>
+      <c r="R18">
+        <v>100</v>
+      </c>
+      <c r="S18">
         <v>80</v>
       </c>
     </row>
-    <row r="19" spans="1:16">
+    <row r="19" spans="1:19">
       <c r="A19" s="1" t="s">
         <v>27</v>
       </c>
@@ -4064,7 +4211,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -4082,7 +4229,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4099,8 +4246,17 @@
       <c r="P19">
         <v>100</v>
       </c>
-    </row>
-    <row r="20" spans="1:16">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>100</v>
+      </c>
+      <c r="S19">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19">
       <c r="A20" s="1" t="s">
         <v>28</v>
       </c>
@@ -4114,7 +4270,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -4132,7 +4288,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -4149,8 +4305,17 @@
       <c r="P20">
         <v>100</v>
       </c>
-    </row>
-    <row r="21" spans="1:16">
+      <c r="Q20">
+        <v>0</v>
+      </c>
+      <c r="R20">
+        <v>100</v>
+      </c>
+      <c r="S20">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="21" spans="1:19">
       <c r="A21" s="1" t="s">
         <v>29</v>
       </c>
@@ -4164,7 +4329,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4182,7 +4347,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4199,8 +4364,17 @@
       <c r="P21">
         <v>100</v>
       </c>
-    </row>
-    <row r="22" spans="1:16">
+      <c r="Q21">
+        <v>0</v>
+      </c>
+      <c r="R21">
+        <v>100</v>
+      </c>
+      <c r="S21">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19">
       <c r="A22" s="1" t="s">
         <v>30</v>
       </c>
@@ -4214,7 +4388,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -4232,7 +4406,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -4249,8 +4423,17 @@
       <c r="P22">
         <v>100</v>
       </c>
-    </row>
-    <row r="23" spans="1:16">
+      <c r="Q22">
+        <v>0</v>
+      </c>
+      <c r="R22">
+        <v>100</v>
+      </c>
+      <c r="S22">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19">
       <c r="A23" s="1" t="s">
         <v>31</v>
       </c>
@@ -4264,7 +4447,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -4282,7 +4465,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4299,8 +4482,17 @@
       <c r="P23">
         <v>100</v>
       </c>
-    </row>
-    <row r="24" spans="1:16">
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>100</v>
+      </c>
+      <c r="S23">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" spans="1:19">
       <c r="A24" s="1" t="s">
         <v>32</v>
       </c>
@@ -4314,7 +4506,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4332,7 +4524,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4349,8 +4541,17 @@
       <c r="P24">
         <v>100</v>
       </c>
-    </row>
-    <row r="25" spans="1:16">
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>100</v>
+      </c>
+      <c r="S24">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19">
       <c r="A25" s="1" t="s">
         <v>33</v>
       </c>
@@ -4364,7 +4565,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4382,7 +4583,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -4399,8 +4600,17 @@
       <c r="P25">
         <v>100</v>
       </c>
-    </row>
-    <row r="26" spans="1:16">
+      <c r="Q25">
+        <v>0</v>
+      </c>
+      <c r="R25">
+        <v>100</v>
+      </c>
+      <c r="S25">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19">
       <c r="A26" s="1" t="s">
         <v>34</v>
       </c>
@@ -4408,31 +4618,40 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F26">
+        <v>100</v>
+      </c>
+      <c r="G26">
         <v>80</v>
       </c>
-      <c r="G26">
-        <v>100</v>
-      </c>
-      <c r="J26">
+      <c r="H26">
         <v>100</v>
       </c>
       <c r="K26">
+        <v>0</v>
+      </c>
+      <c r="L26">
+        <v>100</v>
+      </c>
+      <c r="M26">
         <v>80</v>
       </c>
-      <c r="L26">
-        <v>100</v>
-      </c>
-      <c r="O26">
-        <v>100</v>
-      </c>
-      <c r="P26">
+      <c r="N26">
+        <v>100</v>
+      </c>
+      <c r="Q26">
+        <v>0</v>
+      </c>
+      <c r="R26">
+        <v>100</v>
+      </c>
+      <c r="S26">
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:16">
+    <row r="27" spans="1:19">
       <c r="A27" s="1" t="s">
         <v>35</v>
       </c>
@@ -4446,7 +4665,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -4464,7 +4683,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4481,8 +4700,17 @@
       <c r="P27">
         <v>100</v>
       </c>
-    </row>
-    <row r="28" spans="1:16">
+      <c r="Q27">
+        <v>0</v>
+      </c>
+      <c r="R27">
+        <v>100</v>
+      </c>
+      <c r="S27">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19">
       <c r="A28" s="1" t="s">
         <v>36</v>
       </c>
@@ -4496,7 +4724,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -4514,7 +4742,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4531,8 +4759,17 @@
       <c r="P28">
         <v>100</v>
       </c>
-    </row>
-    <row r="29" spans="1:16">
+      <c r="Q28">
+        <v>0</v>
+      </c>
+      <c r="R28">
+        <v>100</v>
+      </c>
+      <c r="S28">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19">
       <c r="A29" s="1" t="s">
         <v>37</v>
       </c>
@@ -4546,7 +4783,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -4564,7 +4801,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -4581,8 +4818,17 @@
       <c r="P29">
         <v>100</v>
       </c>
-    </row>
-    <row r="30" spans="1:16">
+      <c r="Q29">
+        <v>0</v>
+      </c>
+      <c r="R29">
+        <v>100</v>
+      </c>
+      <c r="S29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19">
       <c r="A30" s="1" t="s">
         <v>38</v>
       </c>
@@ -4596,7 +4842,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -4614,7 +4860,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -4631,8 +4877,17 @@
       <c r="P30">
         <v>100</v>
       </c>
-    </row>
-    <row r="31" spans="1:16">
+      <c r="Q30">
+        <v>0</v>
+      </c>
+      <c r="R30">
+        <v>100</v>
+      </c>
+      <c r="S30">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19">
       <c r="A31" s="1" t="s">
         <v>39</v>
       </c>
@@ -4646,7 +4901,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -4664,7 +4919,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -4681,8 +4936,17 @@
       <c r="P31">
         <v>100</v>
       </c>
-    </row>
-    <row r="32" spans="1:16">
+      <c r="Q31">
+        <v>0</v>
+      </c>
+      <c r="R31">
+        <v>100</v>
+      </c>
+      <c r="S31">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19">
       <c r="A32" s="1" t="s">
         <v>40</v>
       </c>
@@ -4696,7 +4960,7 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -4714,7 +4978,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -4731,8 +4995,17 @@
       <c r="P32">
         <v>100</v>
       </c>
-    </row>
-    <row r="33" spans="1:16">
+      <c r="Q32">
+        <v>0</v>
+      </c>
+      <c r="R32">
+        <v>100</v>
+      </c>
+      <c r="S32">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19">
       <c r="A33" s="1" t="s">
         <v>41</v>
       </c>
@@ -4746,7 +5019,7 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -4764,7 +5037,7 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -4779,14 +5052,23 @@
         <v>100</v>
       </c>
       <c r="P33">
+        <v>100</v>
+      </c>
+      <c r="Q33">
+        <v>0</v>
+      </c>
+      <c r="R33">
+        <v>100</v>
+      </c>
+      <c r="S33">
         <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="B1:F1"/>
-    <mergeCell ref="G1:K1"/>
-    <mergeCell ref="L1:P1"/>
+    <mergeCell ref="B1:G1"/>
+    <mergeCell ref="H1:M1"/>
+    <mergeCell ref="N1:S1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/grupos/3AEM - Estadisticos 20231.xlsx
+++ b/grupos/3AEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="443" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="81">
   <si>
     <t>Materia</t>
   </si>
@@ -182,21 +182,21 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Rivera Cruz Ezequiel</t>
+  </si>
+  <si>
+    <t>Avila Coronado Julieta</t>
+  </si>
+  <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
     <t>González Altamirano Victorino Juventino</t>
   </si>
   <si>
-    <t>Rivera Cruz Ezequiel</t>
-  </si>
-  <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
-    <t>Avila Coronado Julieta</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,27 +209,9 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>ALVAREZ</t>
-  </si>
-  <si>
-    <t>APALE</t>
-  </si>
-  <si>
-    <t>ARGUELLES</t>
-  </si>
-  <si>
-    <t>AGUILAR</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
     <t>BAUTISTA</t>
   </si>
   <si>
-    <t>CORTES</t>
-  </si>
-  <si>
     <t>CRUZ</t>
   </si>
   <si>
@@ -239,199 +221,46 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>DE LA LUZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MERINO</t>
-  </si>
-  <si>
-    <t>PANZO</t>
-  </si>
-  <si>
-    <t>PERALTA</t>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>DE JESUS</t>
+  </si>
+  <si>
+    <t>COYOHUA</t>
+  </si>
+  <si>
+    <t>DIAZ</t>
+  </si>
+  <si>
+    <t>QUERO</t>
+  </si>
+  <si>
+    <t>AVELINO</t>
   </si>
   <si>
     <t>RAMOS</t>
   </si>
   <si>
-    <t>REYES</t>
-  </si>
-  <si>
-    <t>RIOS</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TREJO</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>TEXOCO</t>
-  </si>
-  <si>
-    <t>ROMAN</t>
-  </si>
-  <si>
-    <t>ESTEVEZ</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
-  </si>
-  <si>
-    <t>ROJAS</t>
-  </si>
-  <si>
-    <t>COYOHUA</t>
-  </si>
-  <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>ANGEL</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>VELAZQUEZ</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>AVELINO</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>ZARATE</t>
-  </si>
-  <si>
-    <t>MACARIO</t>
-  </si>
-  <si>
-    <t>LORENZO</t>
-  </si>
-  <si>
-    <t>JOAQUIN</t>
-  </si>
-  <si>
-    <t>GALVAN</t>
-  </si>
-  <si>
-    <t>CAMPOS</t>
-  </si>
-  <si>
-    <t>GILES</t>
-  </si>
-  <si>
-    <t>CERVANTES</t>
-  </si>
-  <si>
-    <t>RUBEN DE JESUS</t>
-  </si>
-  <si>
-    <t>DANIEL</t>
-  </si>
-  <si>
-    <t>CHRISTOPHER</t>
-  </si>
-  <si>
-    <t>RICARDO</t>
-  </si>
-  <si>
     <t>EDER</t>
   </si>
   <si>
-    <t>LUIS FERNANDO</t>
-  </si>
-  <si>
     <t>DIEGO</t>
   </si>
   <si>
     <t>CRISTHIAN</t>
   </si>
   <si>
-    <t>ISABEL</t>
-  </si>
-  <si>
     <t>DIEGO JESUS</t>
   </si>
   <si>
-    <t>JESUS YAEL</t>
-  </si>
-  <si>
-    <t>GABAEL</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
     <t>KEVIN</t>
   </si>
   <si>
-    <t>ALEXANDER</t>
-  </si>
-  <si>
-    <t>RAFAEL</t>
-  </si>
-  <si>
-    <t>OSMAR UZIEL</t>
-  </si>
-  <si>
-    <t>CESAR</t>
-  </si>
-  <si>
-    <t>SHERLIN</t>
-  </si>
-  <si>
-    <t>VALENTINA</t>
-  </si>
-  <si>
-    <t>DYLAN OSMAR</t>
-  </si>
-  <si>
-    <t>GABRIEL</t>
-  </si>
-  <si>
-    <t>GREGORIO</t>
-  </si>
-  <si>
-    <t>SAUL AZAEL</t>
-  </si>
-  <si>
     <t>ANGEL GUILLERMO</t>
-  </si>
-  <si>
-    <t>FERNANDO</t>
-  </si>
-  <si>
-    <t>ISAAC JOHAMET</t>
-  </si>
-  <si>
-    <t>CHRISTOPHER ANDRUS</t>
   </si>
 </sst>
 </file>
@@ -930,7 +759,7 @@
         <v>10</v>
       </c>
       <c r="E4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F4">
         <v>10</v>
@@ -942,19 +771,19 @@
         <v>-1</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -984,7 +813,7 @@
         <v>10</v>
       </c>
       <c r="W4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X4">
         <v>10</v>
@@ -1007,7 +836,7 @@
         <v>8</v>
       </c>
       <c r="E5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F5">
         <v>10</v>
@@ -1019,19 +848,19 @@
         <v>-1</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1055,13 +884,13 @@
         <v>7</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V5">
         <v>8</v>
       </c>
       <c r="W5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
@@ -1084,7 +913,7 @@
         <v>8</v>
       </c>
       <c r="E6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F6">
         <v>7</v>
@@ -1096,19 +925,19 @@
         <v>-1</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1132,19 +961,19 @@
         <v>6</v>
       </c>
       <c r="U6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V6">
         <v>8</v>
       </c>
       <c r="W6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X6">
         <v>7</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1161,7 +990,7 @@
         <v>9</v>
       </c>
       <c r="E7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -1173,19 +1002,19 @@
         <v>-1</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1212,10 +1041,10 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
@@ -1238,7 +1067,7 @@
         <v>9</v>
       </c>
       <c r="E8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F8">
         <v>10</v>
@@ -1250,19 +1079,19 @@
         <v>-1</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1286,13 +1115,13 @@
         <v>8</v>
       </c>
       <c r="U8">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1315,7 +1144,7 @@
         <v>8</v>
       </c>
       <c r="E9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F9">
         <v>8</v>
@@ -1327,19 +1156,19 @@
         <v>-1</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N9">
         <v>-1</v>
@@ -1363,19 +1192,19 @@
         <v>5</v>
       </c>
       <c r="U9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1392,7 +1221,7 @@
         <v>10</v>
       </c>
       <c r="E10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F10">
         <v>8</v>
@@ -1404,19 +1233,19 @@
         <v>-1</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N10">
         <v>-1</v>
@@ -1440,16 +1269,16 @@
         <v>8</v>
       </c>
       <c r="U10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1469,7 +1298,7 @@
         <v>7</v>
       </c>
       <c r="E11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -1481,19 +1310,19 @@
         <v>-1</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1517,19 +1346,19 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V11">
         <v>7</v>
       </c>
       <c r="W11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X11">
         <v>7</v>
       </c>
       <c r="Y11">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1546,7 +1375,7 @@
         <v>8</v>
       </c>
       <c r="E12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F12">
         <v>9</v>
@@ -1558,19 +1387,19 @@
         <v>-1</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N12">
         <v>-1</v>
@@ -1594,16 +1423,16 @@
         <v>8</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y12">
         <v>10</v>
@@ -1623,7 +1452,7 @@
         <v>8</v>
       </c>
       <c r="E13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F13">
         <v>6</v>
@@ -1635,19 +1464,19 @@
         <v>-1</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1671,13 +1500,13 @@
         <v>5</v>
       </c>
       <c r="U13">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="X13">
         <v>6</v>
@@ -1700,7 +1529,7 @@
         <v>8</v>
       </c>
       <c r="E14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F14">
         <v>7</v>
@@ -1712,19 +1541,19 @@
         <v>-1</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N14">
         <v>-1</v>
@@ -1748,19 +1577,19 @@
         <v>8</v>
       </c>
       <c r="U14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y14">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1777,7 +1606,7 @@
         <v>7</v>
       </c>
       <c r="E15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F15">
         <v>7</v>
@@ -1789,19 +1618,19 @@
         <v>-1</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1825,16 +1654,16 @@
         <v>5</v>
       </c>
       <c r="U15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V15">
         <v>7</v>
       </c>
       <c r="W15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y15">
         <v>7</v>
@@ -1854,7 +1683,7 @@
         <v>9</v>
       </c>
       <c r="E16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F16">
         <v>8</v>
@@ -1866,19 +1695,19 @@
         <v>-1</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1902,16 +1731,16 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V16">
         <v>9</v>
       </c>
       <c r="W16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y16">
         <v>10</v>
@@ -1931,7 +1760,7 @@
         <v>9</v>
       </c>
       <c r="E17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F17">
         <v>7</v>
@@ -1943,19 +1772,19 @@
         <v>-1</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -1979,16 +1808,16 @@
         <v>8</v>
       </c>
       <c r="U17">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -2008,7 +1837,7 @@
         <v>7</v>
       </c>
       <c r="E18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F18">
         <v>9</v>
@@ -2020,19 +1849,19 @@
         <v>-1</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2056,19 +1885,19 @@
         <v>6</v>
       </c>
       <c r="U18">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V18">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X18">
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2085,7 +1914,7 @@
         <v>10</v>
       </c>
       <c r="E19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="F19">
         <v>9</v>
@@ -2097,19 +1926,19 @@
         <v>-1</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2139,7 +1968,7 @@
         <v>10</v>
       </c>
       <c r="W19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X19">
         <v>9</v>
@@ -2162,7 +1991,7 @@
         <v>10</v>
       </c>
       <c r="E20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -2174,19 +2003,19 @@
         <v>-1</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N20">
         <v>-1</v>
@@ -2210,13 +2039,13 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
       </c>
       <c r="W20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X20">
         <v>10</v>
@@ -2239,7 +2068,7 @@
         <v>7</v>
       </c>
       <c r="E21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F21">
         <v>7</v>
@@ -2251,19 +2080,19 @@
         <v>-1</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N21">
         <v>-1</v>
@@ -2287,13 +2116,13 @@
         <v>8</v>
       </c>
       <c r="U21">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X21">
         <v>7</v>
@@ -2316,7 +2145,7 @@
         <v>7</v>
       </c>
       <c r="E22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F22">
         <v>7</v>
@@ -2328,19 +2157,19 @@
         <v>-1</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N22">
         <v>-1</v>
@@ -2364,16 +2193,16 @@
         <v>9</v>
       </c>
       <c r="U22">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V22">
         <v>7</v>
       </c>
       <c r="W22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y22">
         <v>9</v>
@@ -2393,7 +2222,7 @@
         <v>7</v>
       </c>
       <c r="E23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F23">
         <v>10</v>
@@ -2405,19 +2234,19 @@
         <v>-1</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N23">
         <v>-1</v>
@@ -2441,19 +2270,19 @@
         <v>9</v>
       </c>
       <c r="U23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="V23">
         <v>7</v>
       </c>
       <c r="W23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X23">
         <v>10</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2470,7 +2299,7 @@
         <v>9</v>
       </c>
       <c r="E24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F24">
         <v>9</v>
@@ -2482,19 +2311,19 @@
         <v>-1</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2518,13 +2347,13 @@
         <v>9</v>
       </c>
       <c r="U24">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2547,7 +2376,7 @@
         <v>10</v>
       </c>
       <c r="E25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="F25">
         <v>10</v>
@@ -2559,19 +2388,19 @@
         <v>-1</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2595,13 +2424,13 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2618,7 +2447,7 @@
         <v>5</v>
       </c>
       <c r="E26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -2630,13 +2459,13 @@
         <v>-1</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2654,10 +2483,10 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2677,7 +2506,7 @@
         <v>10</v>
       </c>
       <c r="E27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F27">
         <v>10</v>
@@ -2689,19 +2518,19 @@
         <v>-1</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2725,13 +2554,13 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>10</v>
       </c>
       <c r="W27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X27">
         <v>10</v>
@@ -2754,7 +2583,7 @@
         <v>9</v>
       </c>
       <c r="E28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F28">
         <v>10</v>
@@ -2766,19 +2595,19 @@
         <v>-1</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N28">
         <v>-1</v>
@@ -2802,13 +2631,13 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V28">
         <v>9</v>
       </c>
       <c r="W28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2831,7 +2660,7 @@
         <v>9</v>
       </c>
       <c r="E29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F29">
         <v>7</v>
@@ -2843,19 +2672,19 @@
         <v>-1</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2879,16 +2708,16 @@
         <v>8</v>
       </c>
       <c r="U29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X29">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y29">
         <v>9</v>
@@ -2908,7 +2737,7 @@
         <v>6</v>
       </c>
       <c r="E30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F30">
         <v>9</v>
@@ -2920,19 +2749,19 @@
         <v>-1</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -2956,13 +2785,13 @@
         <v>8</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="V30">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="W30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X30">
         <v>9</v>
@@ -2985,7 +2814,7 @@
         <v>10</v>
       </c>
       <c r="E31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="F31">
         <v>10</v>
@@ -2997,19 +2826,19 @@
         <v>-1</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3036,16 +2865,16 @@
         <v>9</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>10</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -3062,7 +2891,7 @@
         <v>10</v>
       </c>
       <c r="E32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="F32">
         <v>10</v>
@@ -3074,19 +2903,19 @@
         <v>-1</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N32">
         <v>-1</v>
@@ -3116,10 +2945,10 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -3139,7 +2968,7 @@
         <v>8</v>
       </c>
       <c r="E33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="F33">
         <v>10</v>
@@ -3151,19 +2980,19 @@
         <v>-1</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3187,13 +3016,13 @@
         <v>9</v>
       </c>
       <c r="U33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
@@ -3326,7 +3155,7 @@
         <v>100</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F4">
         <v>100</v>
@@ -3344,7 +3173,7 @@
         <v>100</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L4">
         <v>100</v>
@@ -3362,7 +3191,7 @@
         <v>100</v>
       </c>
       <c r="Q4">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R4">
         <v>100</v>
@@ -3385,7 +3214,7 @@
         <v>100</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F5">
         <v>100</v>
@@ -3403,7 +3232,7 @@
         <v>100</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L5">
         <v>100</v>
@@ -3421,7 +3250,7 @@
         <v>100</v>
       </c>
       <c r="Q5">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R5">
         <v>100</v>
@@ -3444,7 +3273,7 @@
         <v>100</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F6">
         <v>100</v>
@@ -3462,7 +3291,7 @@
         <v>100</v>
       </c>
       <c r="K6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L6">
         <v>100</v>
@@ -3480,7 +3309,7 @@
         <v>100</v>
       </c>
       <c r="Q6">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R6">
         <v>100</v>
@@ -3503,7 +3332,7 @@
         <v>100</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F7">
         <v>100</v>
@@ -3521,7 +3350,7 @@
         <v>100</v>
       </c>
       <c r="K7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L7">
         <v>100</v>
@@ -3539,7 +3368,7 @@
         <v>100</v>
       </c>
       <c r="Q7">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R7">
         <v>100</v>
@@ -3562,7 +3391,7 @@
         <v>100</v>
       </c>
       <c r="E8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F8">
         <v>100</v>
@@ -3580,7 +3409,7 @@
         <v>100</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L8">
         <v>100</v>
@@ -3598,7 +3427,7 @@
         <v>100</v>
       </c>
       <c r="Q8">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R8">
         <v>100</v>
@@ -3621,7 +3450,7 @@
         <v>100</v>
       </c>
       <c r="E9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F9">
         <v>100</v>
@@ -3633,13 +3462,13 @@
         <v>100</v>
       </c>
       <c r="I9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="J9">
         <v>100</v>
       </c>
       <c r="K9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L9">
         <v>100</v>
@@ -3651,13 +3480,13 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="P9">
         <v>100</v>
       </c>
       <c r="Q9">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R9">
         <v>100</v>
@@ -3680,7 +3509,7 @@
         <v>100</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F10">
         <v>100</v>
@@ -3698,7 +3527,7 @@
         <v>100</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L10">
         <v>100</v>
@@ -3716,7 +3545,7 @@
         <v>100</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R10">
         <v>100</v>
@@ -3739,7 +3568,7 @@
         <v>100</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F11">
         <v>100</v>
@@ -3757,7 +3586,7 @@
         <v>100</v>
       </c>
       <c r="K11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L11">
         <v>100</v>
@@ -3775,7 +3604,7 @@
         <v>100</v>
       </c>
       <c r="Q11">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R11">
         <v>100</v>
@@ -3798,7 +3627,7 @@
         <v>100</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F12">
         <v>100</v>
@@ -3816,7 +3645,7 @@
         <v>100</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L12">
         <v>100</v>
@@ -3834,7 +3663,7 @@
         <v>100</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R12">
         <v>100</v>
@@ -3857,7 +3686,7 @@
         <v>100</v>
       </c>
       <c r="E13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F13">
         <v>100</v>
@@ -3869,13 +3698,13 @@
         <v>100</v>
       </c>
       <c r="I13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="J13">
         <v>100</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L13">
         <v>100</v>
@@ -3887,13 +3716,13 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>95</v>
+        <v>97.5</v>
       </c>
       <c r="P13">
         <v>100</v>
       </c>
       <c r="Q13">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R13">
         <v>100</v>
@@ -3916,7 +3745,7 @@
         <v>100</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F14">
         <v>100</v>
@@ -3934,7 +3763,7 @@
         <v>100</v>
       </c>
       <c r="K14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L14">
         <v>100</v>
@@ -3952,7 +3781,7 @@
         <v>100</v>
       </c>
       <c r="Q14">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R14">
         <v>100</v>
@@ -3975,7 +3804,7 @@
         <v>100</v>
       </c>
       <c r="E15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F15">
         <v>100</v>
@@ -3993,7 +3822,7 @@
         <v>100</v>
       </c>
       <c r="K15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L15">
         <v>100</v>
@@ -4011,7 +3840,7 @@
         <v>100</v>
       </c>
       <c r="Q15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R15">
         <v>100</v>
@@ -4034,7 +3863,7 @@
         <v>100</v>
       </c>
       <c r="E16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F16">
         <v>100</v>
@@ -4052,7 +3881,7 @@
         <v>100</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L16">
         <v>100</v>
@@ -4070,7 +3899,7 @@
         <v>100</v>
       </c>
       <c r="Q16">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R16">
         <v>100</v>
@@ -4093,7 +3922,7 @@
         <v>100</v>
       </c>
       <c r="E17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F17">
         <v>100</v>
@@ -4111,7 +3940,7 @@
         <v>100</v>
       </c>
       <c r="K17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L17">
         <v>100</v>
@@ -4129,7 +3958,7 @@
         <v>100</v>
       </c>
       <c r="Q17">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R17">
         <v>100</v>
@@ -4152,7 +3981,7 @@
         <v>100</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F18">
         <v>100</v>
@@ -4170,13 +3999,13 @@
         <v>100</v>
       </c>
       <c r="K18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L18">
         <v>100</v>
       </c>
       <c r="M18">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="N18">
         <v>100</v>
@@ -4188,13 +4017,13 @@
         <v>100</v>
       </c>
       <c r="Q18">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R18">
         <v>100</v>
       </c>
       <c r="S18">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4211,7 +4040,7 @@
         <v>100</v>
       </c>
       <c r="E19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F19">
         <v>100</v>
@@ -4229,7 +4058,7 @@
         <v>100</v>
       </c>
       <c r="K19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L19">
         <v>100</v>
@@ -4247,7 +4076,7 @@
         <v>100</v>
       </c>
       <c r="Q19">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R19">
         <v>100</v>
@@ -4270,7 +4099,7 @@
         <v>100</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F20">
         <v>100</v>
@@ -4288,7 +4117,7 @@
         <v>100</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L20">
         <v>100</v>
@@ -4306,7 +4135,7 @@
         <v>100</v>
       </c>
       <c r="Q20">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R20">
         <v>100</v>
@@ -4329,7 +4158,7 @@
         <v>100</v>
       </c>
       <c r="E21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F21">
         <v>100</v>
@@ -4347,7 +4176,7 @@
         <v>100</v>
       </c>
       <c r="K21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L21">
         <v>100</v>
@@ -4365,7 +4194,7 @@
         <v>100</v>
       </c>
       <c r="Q21">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -4388,7 +4217,7 @@
         <v>100</v>
       </c>
       <c r="E22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F22">
         <v>100</v>
@@ -4406,7 +4235,7 @@
         <v>100</v>
       </c>
       <c r="K22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L22">
         <v>100</v>
@@ -4424,7 +4253,7 @@
         <v>100</v>
       </c>
       <c r="Q22">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R22">
         <v>100</v>
@@ -4447,7 +4276,7 @@
         <v>100</v>
       </c>
       <c r="E23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F23">
         <v>100</v>
@@ -4465,7 +4294,7 @@
         <v>100</v>
       </c>
       <c r="K23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L23">
         <v>100</v>
@@ -4483,7 +4312,7 @@
         <v>100</v>
       </c>
       <c r="Q23">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R23">
         <v>100</v>
@@ -4506,7 +4335,7 @@
         <v>100</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F24">
         <v>100</v>
@@ -4524,7 +4353,7 @@
         <v>100</v>
       </c>
       <c r="K24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L24">
         <v>100</v>
@@ -4542,7 +4371,7 @@
         <v>100</v>
       </c>
       <c r="Q24">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R24">
         <v>100</v>
@@ -4565,7 +4394,7 @@
         <v>100</v>
       </c>
       <c r="E25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F25">
         <v>100</v>
@@ -4583,7 +4412,7 @@
         <v>100</v>
       </c>
       <c r="K25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L25">
         <v>100</v>
@@ -4601,7 +4430,7 @@
         <v>100</v>
       </c>
       <c r="Q25">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R25">
         <v>100</v>
@@ -4618,7 +4447,7 @@
         <v>100</v>
       </c>
       <c r="E26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F26">
         <v>100</v>
@@ -4630,7 +4459,7 @@
         <v>100</v>
       </c>
       <c r="K26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L26">
         <v>100</v>
@@ -4642,7 +4471,7 @@
         <v>100</v>
       </c>
       <c r="Q26">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R26">
         <v>100</v>
@@ -4665,7 +4494,7 @@
         <v>100</v>
       </c>
       <c r="E27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F27">
         <v>100</v>
@@ -4683,7 +4512,7 @@
         <v>100</v>
       </c>
       <c r="K27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L27">
         <v>100</v>
@@ -4701,7 +4530,7 @@
         <v>100</v>
       </c>
       <c r="Q27">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R27">
         <v>100</v>
@@ -4724,7 +4553,7 @@
         <v>100</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F28">
         <v>100</v>
@@ -4742,7 +4571,7 @@
         <v>100</v>
       </c>
       <c r="K28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L28">
         <v>100</v>
@@ -4760,7 +4589,7 @@
         <v>100</v>
       </c>
       <c r="Q28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R28">
         <v>100</v>
@@ -4783,7 +4612,7 @@
         <v>100</v>
       </c>
       <c r="E29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F29">
         <v>100</v>
@@ -4801,7 +4630,7 @@
         <v>100</v>
       </c>
       <c r="K29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L29">
         <v>100</v>
@@ -4819,7 +4648,7 @@
         <v>100</v>
       </c>
       <c r="Q29">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R29">
         <v>100</v>
@@ -4842,7 +4671,7 @@
         <v>100</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F30">
         <v>100</v>
@@ -4860,7 +4689,7 @@
         <v>100</v>
       </c>
       <c r="K30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L30">
         <v>100</v>
@@ -4878,7 +4707,7 @@
         <v>100</v>
       </c>
       <c r="Q30">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R30">
         <v>100</v>
@@ -4901,7 +4730,7 @@
         <v>100</v>
       </c>
       <c r="E31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F31">
         <v>100</v>
@@ -4919,7 +4748,7 @@
         <v>100</v>
       </c>
       <c r="K31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L31">
         <v>100</v>
@@ -4937,7 +4766,7 @@
         <v>100</v>
       </c>
       <c r="Q31">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R31">
         <v>100</v>
@@ -4960,7 +4789,7 @@
         <v>100</v>
       </c>
       <c r="E32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F32">
         <v>100</v>
@@ -4978,7 +4807,7 @@
         <v>100</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L32">
         <v>100</v>
@@ -4996,7 +4825,7 @@
         <v>100</v>
       </c>
       <c r="Q32">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R32">
         <v>100</v>
@@ -5019,7 +4848,7 @@
         <v>100</v>
       </c>
       <c r="E33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F33">
         <v>100</v>
@@ -5037,7 +4866,7 @@
         <v>100</v>
       </c>
       <c r="K33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="L33">
         <v>100</v>
@@ -5055,7 +4884,7 @@
         <v>100</v>
       </c>
       <c r="Q33">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="R33">
         <v>100</v>
@@ -5118,7 +4947,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>54</v>
@@ -5127,27 +4956,30 @@
         <v>30</v>
       </c>
       <c r="D2">
+        <v>24</v>
+      </c>
+      <c r="E2">
+        <v>6</v>
+      </c>
+      <c r="F2" s="2">
+        <v>80</v>
+      </c>
+      <c r="G2" s="2">
+        <v>20</v>
+      </c>
+      <c r="H2">
+        <v>7.8</v>
+      </c>
+      <c r="I2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="J2" s="2">
         <v>0</v>
-      </c>
-      <c r="F2" s="2">
-        <v>0</v>
-      </c>
-      <c r="G2" s="2">
-        <v>0</v>
-      </c>
-      <c r="I2">
-        <v>30</v>
-      </c>
-      <c r="J2" s="2">
-        <v>100</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
@@ -5156,19 +4988,19 @@
         <v>29</v>
       </c>
       <c r="D3">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="E3">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>75.90000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="G3" s="2">
-        <v>24.1</v>
+        <v>3.4</v>
       </c>
       <c r="H3">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5179,7 +5011,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
@@ -5188,19 +5020,19 @@
         <v>30</v>
       </c>
       <c r="D4">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F4" s="2">
-        <v>80</v>
+        <v>96.7</v>
       </c>
       <c r="G4" s="2">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="H4">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5211,7 +5043,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
@@ -5232,7 +5064,7 @@
         <v>3.3</v>
       </c>
       <c r="H5">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5243,7 +5075,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
@@ -5264,7 +5096,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5275,10 +5107,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -5296,7 +5128,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5312,7 +5144,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5339,606 +5171,6 @@
         <v>11</v>
       </c>
     </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>22330051920002</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
-      </c>
-      <c r="C2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>22330051920003</v>
-      </c>
-      <c r="B3" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>22330051920004</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
-      </c>
-      <c r="C4" t="s">
-        <v>89</v>
-      </c>
-      <c r="D4" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>22330051920001</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>85</v>
-      </c>
-      <c r="D5" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>22330051920005</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>90</v>
-      </c>
-      <c r="D6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>22330051920006</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>91</v>
-      </c>
-      <c r="D7" t="s">
-        <v>114</v>
-      </c>
-      <c r="E7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>22330051920009</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>92</v>
-      </c>
-      <c r="D8" t="s">
-        <v>115</v>
-      </c>
-      <c r="E8" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>22330051920010</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>93</v>
-      </c>
-      <c r="D9" t="s">
-        <v>116</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>22330051920013</v>
-      </c>
-      <c r="B10" t="s">
-        <v>71</v>
-      </c>
-      <c r="C10" t="s">
-        <v>94</v>
-      </c>
-      <c r="D10" t="s">
-        <v>117</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>22330051920014</v>
-      </c>
-      <c r="B11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D11" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>22330051920015</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>96</v>
-      </c>
-      <c r="D12" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>22330051920016</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>97</v>
-      </c>
-      <c r="D13" t="s">
-        <v>120</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>22330051920320</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>98</v>
-      </c>
-      <c r="D14" t="s">
-        <v>121</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>22330051920017</v>
-      </c>
-      <c r="B15" t="s">
-        <v>74</v>
-      </c>
-      <c r="C15" t="s">
-        <v>99</v>
-      </c>
-      <c r="D15" t="s">
-        <v>122</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>22330051920018</v>
-      </c>
-      <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" t="s">
-        <v>100</v>
-      </c>
-      <c r="D16" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>22330051920012</v>
-      </c>
-      <c r="B17" t="s">
-        <v>76</v>
-      </c>
-      <c r="C17" t="s">
-        <v>85</v>
-      </c>
-      <c r="D17" t="s">
-        <v>124</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>22330051920020</v>
-      </c>
-      <c r="B18" t="s">
-        <v>77</v>
-      </c>
-      <c r="C18" t="s">
-        <v>101</v>
-      </c>
-      <c r="D18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>22330051920382</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>102</v>
-      </c>
-      <c r="D19" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>22330051920022</v>
-      </c>
-      <c r="B20" t="s">
-        <v>78</v>
-      </c>
-      <c r="C20" t="s">
-        <v>85</v>
-      </c>
-      <c r="D20" t="s">
-        <v>127</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>22330051920322</v>
-      </c>
-      <c r="B21" t="s">
-        <v>79</v>
-      </c>
-      <c r="C21" t="s">
-        <v>103</v>
-      </c>
-      <c r="D21" t="s">
-        <v>128</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>22330051920023</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23">
-        <v>22330051920024</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24">
-        <v>20330051920059</v>
-      </c>
-      <c r="B24" t="s">
-        <v>82</v>
-      </c>
-      <c r="C24" t="s">
-        <v>105</v>
-      </c>
-      <c r="D24" t="s">
-        <v>111</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25">
-        <v>22330051920025</v>
-      </c>
-      <c r="B25" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" t="s">
-        <v>106</v>
-      </c>
-      <c r="D25" t="s">
-        <v>131</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26">
-        <v>22330051920326</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
-      </c>
-      <c r="D26" t="s">
-        <v>132</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27">
-        <v>22330051920026</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>108</v>
-      </c>
-      <c r="D27" t="s">
-        <v>133</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28">
-        <v>22330051920173</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>81</v>
-      </c>
-      <c r="D28" t="s">
-        <v>134</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29">
-        <v>22330051920330</v>
-      </c>
-      <c r="B29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C29" t="s">
-        <v>85</v>
-      </c>
-      <c r="D29" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6">
-      <c r="A30">
-        <v>22330051920027</v>
-      </c>
-      <c r="B30" t="s">
-        <v>85</v>
-      </c>
-      <c r="C30" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" t="s">
-        <v>136</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31">
-        <v>22330051920332</v>
-      </c>
-      <c r="B31" t="s">
-        <v>86</v>
-      </c>
-      <c r="C31" t="s">
-        <v>77</v>
-      </c>
-      <c r="D31" t="s">
-        <v>137</v>
-      </c>
-      <c r="E31" t="s">
-        <v>8</v>
-      </c>
-      <c r="F31" t="s">
-        <v>54</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -5946,7 +5178,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5978,22 +5210,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920009</v>
+        <v>22330051920006</v>
       </c>
       <c r="B2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" t="s">
         <v>69</v>
       </c>
-      <c r="C2" t="s">
-        <v>92</v>
-      </c>
       <c r="D2" t="s">
-        <v>115</v>
+        <v>75</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -6001,45 +5233,45 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920009</v>
+        <v>22330051920010</v>
       </c>
       <c r="B3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="C3" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="D3" t="s">
-        <v>115</v>
+        <v>76</v>
       </c>
       <c r="E3" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F3" t="s">
         <v>54</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920017</v>
+        <v>22330051920013</v>
       </c>
       <c r="B4" t="s">
-        <v>74</v>
+        <v>65</v>
       </c>
       <c r="C4" t="s">
-        <v>99</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>122</v>
+        <v>77</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -6047,25 +5279,25 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>22330051920017</v>
+        <v>22330051920015</v>
       </c>
       <c r="B5" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>99</v>
+        <v>72</v>
       </c>
       <c r="D5" t="s">
-        <v>122</v>
+        <v>78</v>
       </c>
       <c r="E5" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F5" t="s">
         <v>54</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -6073,19 +5305,19 @@
         <v>22330051920018</v>
       </c>
       <c r="B6" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>100</v>
+        <v>73</v>
       </c>
       <c r="D6" t="s">
-        <v>123</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G6">
         <v>5</v>
@@ -6093,554 +5325,25 @@
     </row>
     <row r="7" spans="1:7">
       <c r="A7">
-        <v>22330051920018</v>
+        <v>22330051920173</v>
       </c>
       <c r="B7" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
       <c r="D7" t="s">
-        <v>123</v>
+        <v>80</v>
       </c>
       <c r="E7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F7" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>22330051920322</v>
-      </c>
-      <c r="B8" t="s">
-        <v>79</v>
-      </c>
-      <c r="C8" t="s">
-        <v>103</v>
-      </c>
-      <c r="D8" t="s">
-        <v>128</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
         <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>22330051920322</v>
-      </c>
-      <c r="B9" t="s">
-        <v>79</v>
-      </c>
-      <c r="C9" t="s">
-        <v>103</v>
-      </c>
-      <c r="D9" t="s">
-        <v>128</v>
-      </c>
-      <c r="E9" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" t="s">
-        <v>54</v>
-      </c>
-      <c r="G9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>22330051920002</v>
-      </c>
-      <c r="B10" t="s">
-        <v>63</v>
-      </c>
-      <c r="C10" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11">
-        <v>22330051920003</v>
-      </c>
-      <c r="B11" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" t="s">
-        <v>88</v>
-      </c>
-      <c r="D11" t="s">
-        <v>111</v>
-      </c>
-      <c r="E11" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" t="s">
-        <v>54</v>
-      </c>
-      <c r="G11">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12">
-        <v>22330051920004</v>
-      </c>
-      <c r="B12" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" t="s">
-        <v>89</v>
-      </c>
-      <c r="D12" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" t="s">
-        <v>8</v>
-      </c>
-      <c r="F12" t="s">
-        <v>54</v>
-      </c>
-      <c r="G12">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13">
-        <v>22330051920001</v>
-      </c>
-      <c r="B13" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" t="s">
-        <v>85</v>
-      </c>
-      <c r="D13" t="s">
-        <v>112</v>
-      </c>
-      <c r="E13" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" t="s">
-        <v>54</v>
-      </c>
-      <c r="G13">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14">
-        <v>22330051920005</v>
-      </c>
-      <c r="B14" t="s">
-        <v>67</v>
-      </c>
-      <c r="C14" t="s">
-        <v>90</v>
-      </c>
-      <c r="D14" t="s">
-        <v>113</v>
-      </c>
-      <c r="E14" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" t="s">
-        <v>54</v>
-      </c>
-      <c r="G14">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15">
-        <v>22330051920014</v>
-      </c>
-      <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" t="s">
-        <v>95</v>
-      </c>
-      <c r="D15" t="s">
-        <v>118</v>
-      </c>
-      <c r="E15" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" t="s">
-        <v>54</v>
-      </c>
-      <c r="G15">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16">
-        <v>22330051920016</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" t="s">
-        <v>120</v>
-      </c>
-      <c r="E16" t="s">
-        <v>8</v>
-      </c>
-      <c r="F16" t="s">
-        <v>54</v>
-      </c>
-      <c r="G16">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17">
-        <v>22330051920320</v>
-      </c>
-      <c r="B17" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" t="s">
-        <v>98</v>
-      </c>
-      <c r="D17" t="s">
-        <v>121</v>
-      </c>
-      <c r="E17" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" t="s">
-        <v>54</v>
-      </c>
-      <c r="G17">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18">
-        <v>22330051920012</v>
-      </c>
-      <c r="B18" t="s">
-        <v>76</v>
-      </c>
-      <c r="C18" t="s">
-        <v>85</v>
-      </c>
-      <c r="D18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F18" t="s">
-        <v>54</v>
-      </c>
-      <c r="G18">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19">
-        <v>22330051920020</v>
-      </c>
-      <c r="B19" t="s">
-        <v>77</v>
-      </c>
-      <c r="C19" t="s">
-        <v>101</v>
-      </c>
-      <c r="D19" t="s">
-        <v>125</v>
-      </c>
-      <c r="E19" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>54</v>
-      </c>
-      <c r="G19">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20">
-        <v>22330051920382</v>
-      </c>
-      <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" t="s">
-        <v>102</v>
-      </c>
-      <c r="D20" t="s">
-        <v>126</v>
-      </c>
-      <c r="E20" t="s">
-        <v>8</v>
-      </c>
-      <c r="F20" t="s">
-        <v>54</v>
-      </c>
-      <c r="G20">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21">
-        <v>22330051920022</v>
-      </c>
-      <c r="B21" t="s">
-        <v>78</v>
-      </c>
-      <c r="C21" t="s">
-        <v>85</v>
-      </c>
-      <c r="D21" t="s">
-        <v>127</v>
-      </c>
-      <c r="E21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F21" t="s">
-        <v>54</v>
-      </c>
-      <c r="G21">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22">
-        <v>22330051920023</v>
-      </c>
-      <c r="B22" t="s">
-        <v>80</v>
-      </c>
-      <c r="C22" t="s">
-        <v>104</v>
-      </c>
-      <c r="D22" t="s">
-        <v>129</v>
-      </c>
-      <c r="E22" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" t="s">
-        <v>54</v>
-      </c>
-      <c r="G22">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23">
-        <v>22330051920024</v>
-      </c>
-      <c r="B23" t="s">
-        <v>81</v>
-      </c>
-      <c r="C23" t="s">
-        <v>92</v>
-      </c>
-      <c r="D23" t="s">
-        <v>130</v>
-      </c>
-      <c r="E23" t="s">
-        <v>8</v>
-      </c>
-      <c r="F23" t="s">
-        <v>54</v>
-      </c>
-      <c r="G23">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24">
-        <v>22330051920025</v>
-      </c>
-      <c r="B24" t="s">
-        <v>83</v>
-      </c>
-      <c r="C24" t="s">
-        <v>106</v>
-      </c>
-      <c r="D24" t="s">
-        <v>131</v>
-      </c>
-      <c r="E24" t="s">
-        <v>8</v>
-      </c>
-      <c r="F24" t="s">
-        <v>54</v>
-      </c>
-      <c r="G24">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25">
-        <v>22330051920326</v>
-      </c>
-      <c r="B25" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" t="s">
-        <v>107</v>
-      </c>
-      <c r="D25" t="s">
-        <v>132</v>
-      </c>
-      <c r="E25" t="s">
-        <v>8</v>
-      </c>
-      <c r="F25" t="s">
-        <v>54</v>
-      </c>
-      <c r="G25">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26">
-        <v>22330051920026</v>
-      </c>
-      <c r="B26" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" t="s">
-        <v>108</v>
-      </c>
-      <c r="D26" t="s">
-        <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>8</v>
-      </c>
-      <c r="F26" t="s">
-        <v>54</v>
-      </c>
-      <c r="G26">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27">
-        <v>22330051920173</v>
-      </c>
-      <c r="B27" t="s">
-        <v>84</v>
-      </c>
-      <c r="C27" t="s">
-        <v>81</v>
-      </c>
-      <c r="D27" t="s">
-        <v>134</v>
-      </c>
-      <c r="E27" t="s">
-        <v>8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28">
-        <v>22330051920330</v>
-      </c>
-      <c r="B28" t="s">
-        <v>84</v>
-      </c>
-      <c r="C28" t="s">
-        <v>85</v>
-      </c>
-      <c r="D28" t="s">
-        <v>135</v>
-      </c>
-      <c r="E28" t="s">
-        <v>8</v>
-      </c>
-      <c r="F28" t="s">
-        <v>54</v>
-      </c>
-      <c r="G28">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29">
-        <v>22330051920027</v>
-      </c>
-      <c r="B29" t="s">
-        <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>109</v>
-      </c>
-      <c r="D29" t="s">
-        <v>136</v>
-      </c>
-      <c r="E29" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" t="s">
-        <v>54</v>
-      </c>
-      <c r="G29">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30">
-        <v>22330051920332</v>
-      </c>
-      <c r="B30" t="s">
-        <v>86</v>
-      </c>
-      <c r="C30" t="s">
-        <v>77</v>
-      </c>
-      <c r="D30" t="s">
-        <v>137</v>
-      </c>
-      <c r="E30" t="s">
-        <v>8</v>
-      </c>
-      <c r="F30" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30">
-        <v>-1</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3AEM - Estadisticos 20231.xlsx
+++ b/grupos/3AEM - Estadisticos 20231.xlsx
@@ -221,7 +221,7 @@
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERRERA</t>
+    <t>GUERRA</t>
   </si>
   <si>
     <t>ROMERO</t>
@@ -239,7 +239,7 @@
     <t>QUERO</t>
   </si>
   <si>
-    <t>AVELINO</t>
+    <t>JERONIMO</t>
   </si>
   <si>
     <t>RAMOS</t>
@@ -257,7 +257,7 @@
     <t>DIEGO JESUS</t>
   </si>
   <si>
-    <t>KEVIN</t>
+    <t>LUIS</t>
   </si>
   <si>
     <t>ANGEL GUILLERMO</t>
@@ -768,7 +768,7 @@
         <v>10</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>9</v>
@@ -845,7 +845,7 @@
         <v>9</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I5">
         <v>9</v>
@@ -922,7 +922,7 @@
         <v>10</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I6">
         <v>9</v>
@@ -958,7 +958,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U6">
         <v>8</v>
@@ -999,7 +999,7 @@
         <v>9</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>9</v>
@@ -1035,7 +1035,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U7">
         <v>9</v>
@@ -1076,7 +1076,7 @@
         <v>9</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I8">
         <v>9</v>
@@ -1153,7 +1153,7 @@
         <v>8</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I9">
         <v>9</v>
@@ -1230,7 +1230,7 @@
         <v>9</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I10">
         <v>9</v>
@@ -1266,7 +1266,7 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U10">
         <v>7</v>
@@ -1307,7 +1307,7 @@
         <v>8</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I11">
         <v>9</v>
@@ -1384,7 +1384,7 @@
         <v>10</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I12">
         <v>9</v>
@@ -1420,7 +1420,7 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U12">
         <v>8</v>
@@ -1461,7 +1461,7 @@
         <v>8</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I13">
         <v>9</v>
@@ -1538,7 +1538,7 @@
         <v>9</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I14">
         <v>9</v>
@@ -1574,7 +1574,7 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U14">
         <v>8</v>
@@ -1615,7 +1615,7 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="I15">
         <v>9</v>
@@ -1692,7 +1692,7 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I16">
         <v>9</v>
@@ -1769,7 +1769,7 @@
         <v>10</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I17">
         <v>9</v>
@@ -1805,7 +1805,7 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U17">
         <v>8</v>
@@ -1846,7 +1846,7 @@
         <v>6</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I18">
         <v>9</v>
@@ -1882,7 +1882,7 @@
         <v>-1</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U18">
         <v>7</v>
@@ -1923,7 +1923,7 @@
         <v>10</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I19">
         <v>9</v>
@@ -1959,7 +1959,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U19">
         <v>9</v>
@@ -2000,7 +2000,7 @@
         <v>10</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I20">
         <v>9</v>
@@ -2036,7 +2036,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U20">
         <v>8</v>
@@ -2077,7 +2077,7 @@
         <v>9</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>9</v>
@@ -2154,7 +2154,7 @@
         <v>9</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I22">
         <v>9</v>
@@ -2231,7 +2231,7 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>9</v>
@@ -2308,7 +2308,7 @@
         <v>10</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I24">
         <v>9</v>
@@ -2385,7 +2385,7 @@
         <v>9</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I25">
         <v>9</v>
@@ -2456,7 +2456,7 @@
         <v>5</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K26">
         <v>6</v>
@@ -2515,7 +2515,7 @@
         <v>10</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
         <v>9</v>
@@ -2592,7 +2592,7 @@
         <v>10</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I28">
         <v>9</v>
@@ -2669,7 +2669,7 @@
         <v>9</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I29">
         <v>9</v>
@@ -2746,7 +2746,7 @@
         <v>9</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
         <v>9</v>
@@ -2782,7 +2782,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U30">
         <v>8</v>
@@ -2823,7 +2823,7 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <v>9</v>
@@ -2859,7 +2859,7 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>9</v>
@@ -2900,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -2977,7 +2977,7 @@
         <v>8</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
         <v>9</v>
@@ -4968,7 +4968,7 @@
         <v>20</v>
       </c>
       <c r="H2">
-        <v>7.8</v>
+        <v>8.1</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -5302,7 +5302,7 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>22330051920018</v>
+        <v>22330051920017</v>
       </c>
       <c r="B6" t="s">
         <v>67</v>

--- a/grupos/3AEM - Estadisticos 20231.xlsx
+++ b/grupos/3AEM - Estadisticos 20231.xlsx
@@ -2900,7 +2900,7 @@
         <v>10</v>
       </c>
       <c r="H32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="I32">
         <v>9</v>
@@ -2936,7 +2936,7 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U32">
         <v>10</v>
@@ -4968,7 +4968,7 @@
         <v>20</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>

--- a/grupos/3AEM - Estadisticos 20231.xlsx
+++ b/grupos/3AEM - Estadisticos 20231.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="178" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="69">
   <si>
     <t>Materia</t>
   </si>
@@ -185,18 +185,18 @@
     <t>Rivera Cruz Ezequiel</t>
   </si>
   <si>
+    <t>Castro Vasquez Julieta</t>
+  </si>
+  <si>
+    <t>González Altamirano Victorino Juventino</t>
+  </si>
+  <si>
     <t>Avila Coronado Julieta</t>
   </si>
   <si>
-    <t>Castro Vasquez Julieta</t>
-  </si>
-  <si>
     <t>Torres Sánchez José Luis</t>
   </si>
   <si>
-    <t>González Altamirano Victorino Juventino</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -209,58 +209,22 @@
     <t>Nombres</t>
   </si>
   <si>
-    <t>BAUTISTA</t>
+    <t>REYES</t>
   </si>
   <si>
     <t>CRUZ</t>
   </si>
   <si>
-    <t>FLORES</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>GUERRA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>DE JESUS</t>
+    <t>JOAQUIN</t>
   </si>
   <si>
     <t>COYOHUA</t>
   </si>
   <si>
-    <t>DIAZ</t>
-  </si>
-  <si>
-    <t>QUERO</t>
-  </si>
-  <si>
-    <t>JERONIMO</t>
-  </si>
-  <si>
-    <t>RAMOS</t>
-  </si>
-  <si>
-    <t>EDER</t>
+    <t>DANIEL</t>
   </si>
   <si>
     <t>DIEGO</t>
-  </si>
-  <si>
-    <t>CRISTHIAN</t>
-  </si>
-  <si>
-    <t>DIEGO JESUS</t>
-  </si>
-  <si>
-    <t>LUIS</t>
-  </si>
-  <si>
-    <t>ANGEL GUILLERMO</t>
   </si>
 </sst>
 </file>
@@ -786,22 +750,22 @@
         <v>9</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T4">
         <v>10</v>
@@ -863,31 +827,31 @@
         <v>8</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>9</v>
@@ -940,28 +904,28 @@
         <v>7</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T6">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V6">
         <v>8</v>
@@ -1017,22 +981,22 @@
         <v>9</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T7">
         <v>9</v>
@@ -1041,7 +1005,7 @@
         <v>9</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
         <v>9</v>
@@ -1094,34 +1058,34 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T8">
         <v>8</v>
       </c>
       <c r="U8">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V8">
         <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
@@ -1171,31 +1135,31 @@
         <v>9</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>8</v>
@@ -1248,22 +1212,22 @@
         <v>9</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T10">
         <v>9</v>
@@ -1278,7 +1242,7 @@
         <v>9</v>
       </c>
       <c r="X10">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y10">
         <v>9</v>
@@ -1325,28 +1289,28 @@
         <v>6</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T11">
         <v>5</v>
       </c>
       <c r="U11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V11">
         <v>7</v>
@@ -1402,34 +1366,34 @@
         <v>9</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T12">
         <v>9</v>
       </c>
       <c r="U12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V12">
         <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1479,31 +1443,31 @@
         <v>7</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>7</v>
@@ -1556,34 +1520,34 @@
         <v>10</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T14">
         <v>9</v>
       </c>
       <c r="U14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
         <v>8</v>
@@ -1633,31 +1597,31 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
@@ -1710,28 +1674,28 @@
         <v>9</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
         <v>9</v>
@@ -1743,7 +1707,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1787,28 +1751,28 @@
         <v>9</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T17">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V17">
         <v>8</v>
@@ -1864,28 +1828,28 @@
         <v>9</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V18">
         <v>8</v>
@@ -1941,40 +1905,40 @@
         <v>9</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T19">
         <v>7</v>
       </c>
       <c r="U19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2018,22 +1982,22 @@
         <v>10</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T20">
         <v>10</v>
@@ -2095,31 +2059,31 @@
         <v>9</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T21">
         <v>8</v>
       </c>
       <c r="U21">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W21">
         <v>9</v>
@@ -2172,31 +2136,31 @@
         <v>9</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T22">
         <v>9</v>
       </c>
       <c r="U22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W22">
         <v>9</v>
@@ -2249,37 +2213,37 @@
         <v>9</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T23">
         <v>9</v>
       </c>
       <c r="U23">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="V23">
         <v>7</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
         <v>9</v>
@@ -2326,22 +2290,22 @@
         <v>9</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T24">
         <v>9</v>
@@ -2350,7 +2314,7 @@
         <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
@@ -2403,28 +2367,28 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T25">
         <v>10</v>
       </c>
       <c r="U25">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
@@ -2468,16 +2432,16 @@
         <v>5</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T26">
         <v>5</v>
@@ -2486,7 +2450,7 @@
         <v>6</v>
       </c>
       <c r="X26">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2533,22 +2497,22 @@
         <v>9</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2610,22 +2574,22 @@
         <v>9</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T28">
         <v>10</v>
@@ -2637,7 +2601,7 @@
         <v>9</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2687,22 +2651,22 @@
         <v>9</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T29">
         <v>8</v>
@@ -2764,31 +2728,31 @@
         <v>8</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T30">
         <v>9</v>
       </c>
       <c r="U30">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="W30">
         <v>8</v>
@@ -2797,7 +2761,7 @@
         <v>9</v>
       </c>
       <c r="Y30">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2841,22 +2805,22 @@
         <v>8</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T31">
         <v>10</v>
@@ -2871,7 +2835,7 @@
         <v>10</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
         <v>9</v>
@@ -2918,22 +2882,22 @@
         <v>9</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T32">
         <v>10</v>
@@ -2945,7 +2909,7 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
         <v>9</v>
@@ -2995,31 +2959,31 @@
         <v>8</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>9</v>
       </c>
       <c r="U33">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W33">
         <v>8</v>
@@ -3480,7 +3444,7 @@
         <v>100</v>
       </c>
       <c r="O9">
-        <v>95</v>
+        <v>91.7</v>
       </c>
       <c r="P9">
         <v>100</v>
@@ -3716,7 +3680,7 @@
         <v>100</v>
       </c>
       <c r="O13">
-        <v>97.5</v>
+        <v>98.3</v>
       </c>
       <c r="P13">
         <v>100</v>
@@ -4023,7 +3987,7 @@
         <v>100</v>
       </c>
       <c r="S18">
-        <v>90</v>
+        <v>93.8</v>
       </c>
     </row>
     <row r="19" spans="1:19">
@@ -4477,7 +4441,7 @@
         <v>100</v>
       </c>
       <c r="S26">
-        <v>80</v>
+        <v>82.8</v>
       </c>
     </row>
     <row r="27" spans="1:19">
@@ -4956,19 +4920,19 @@
         <v>30</v>
       </c>
       <c r="D2">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F2" s="2">
-        <v>80</v>
+        <v>93.3</v>
       </c>
       <c r="G2" s="2">
-        <v>20</v>
+        <v>6.7</v>
       </c>
       <c r="H2">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4979,28 +4943,28 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
         <v>55</v>
       </c>
       <c r="C3">
+        <v>30</v>
+      </c>
+      <c r="D3">
         <v>29</v>
-      </c>
-      <c r="D3">
-        <v>28</v>
       </c>
       <c r="E3">
         <v>1</v>
       </c>
       <c r="F3" s="2">
-        <v>96.59999999999999</v>
+        <v>96.7</v>
       </c>
       <c r="G3" s="2">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="H3">
-        <v>8.4</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -5011,28 +4975,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
         <v>56</v>
       </c>
       <c r="C4">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D4">
         <v>29</v>
       </c>
       <c r="E4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F4" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H4">
-        <v>9</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5043,28 +5007,28 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
         <v>57</v>
       </c>
       <c r="C5">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>29</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F5" s="2">
-        <v>96.7</v>
+        <v>100</v>
       </c>
       <c r="G5" s="2">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5075,16 +5039,16 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>58</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -5096,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.1</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5107,10 +5071,10 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C7">
         <v>30</v>
@@ -5128,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>9</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -5178,7 +5142,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -5210,16 +5174,16 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>22330051920006</v>
+        <v>20330051920059</v>
       </c>
       <c r="B2" t="s">
         <v>63</v>
       </c>
       <c r="C2" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="E2" t="s">
         <v>5</v>
@@ -5233,22 +5197,22 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>22330051920010</v>
+        <v>20330051920059</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3" t="s">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
-        <v>76</v>
+        <v>67</v>
       </c>
       <c r="E3" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>5</v>
@@ -5256,16 +5220,16 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>22330051920013</v>
+        <v>22330051920010</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C4" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>77</v>
+        <v>68</v>
       </c>
       <c r="E4" t="s">
         <v>5</v>
@@ -5274,75 +5238,6 @@
         <v>54</v>
       </c>
       <c r="G4">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>22330051920015</v>
-      </c>
-      <c r="B5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C5" t="s">
-        <v>72</v>
-      </c>
-      <c r="D5" t="s">
-        <v>78</v>
-      </c>
-      <c r="E5" t="s">
-        <v>5</v>
-      </c>
-      <c r="F5" t="s">
-        <v>54</v>
-      </c>
-      <c r="G5">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>22330051920017</v>
-      </c>
-      <c r="B6" t="s">
-        <v>67</v>
-      </c>
-      <c r="C6" t="s">
-        <v>73</v>
-      </c>
-      <c r="D6" t="s">
-        <v>79</v>
-      </c>
-      <c r="E6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>22330051920173</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>74</v>
-      </c>
-      <c r="D7" t="s">
-        <v>80</v>
-      </c>
-      <c r="E7" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3AEM - Estadisticos 20231.xlsx
+++ b/grupos/3AEM - Estadisticos 20231.xlsx
@@ -845,22 +845,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U5">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -922,22 +922,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W6">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X6">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -999,22 +999,22 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X7">
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1076,22 +1076,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U8">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W8">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1153,22 +1153,22 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U9">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y9">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1230,22 +1230,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U10">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X10">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y10">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1310,19 +1310,19 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W11">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y11">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1384,16 +1384,16 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W12">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1461,22 +1461,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W13">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="X13">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y13">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1538,19 +1538,19 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1615,22 +1615,22 @@
         <v>7</v>
       </c>
       <c r="T15">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U15">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W15">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1692,22 +1692,22 @@
         <v>9</v>
       </c>
       <c r="T16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U16">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1769,19 +1769,19 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U17">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X17">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -1846,22 +1846,22 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="U18">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W18">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X18">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1923,22 +1923,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="U19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X19">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y19">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2003,7 +2003,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2077,22 +2077,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X21">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="Y21">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2154,22 +2154,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U22">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W22">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X22">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y22">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2231,22 +2231,22 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U23">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="V23">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X23">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y23">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2308,19 +2308,19 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U24">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2388,19 +2388,19 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2447,10 +2447,10 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="X26">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2518,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2595,13 +2595,13 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W28">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2669,22 +2669,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="U29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="V29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W29">
         <v>10</v>
       </c>
       <c r="X29">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="Y29">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2746,22 +2746,22 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V30">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="W30">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y30">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2826,19 +2826,19 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>10</v>
       </c>
       <c r="X31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y31">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2909,10 +2909,10 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X32">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -2977,22 +2977,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U33">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="V33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="W33">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4932,7 +4932,7 @@
         <v>6.7</v>
       </c>
       <c r="H2">
-        <v>8.300000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4964,7 +4964,7 @@
         <v>3.3</v>
       </c>
       <c r="H3">
-        <v>8.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>7.4</v>
+        <v>10</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5060,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>8.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>10</v>
       </c>
       <c r="I7">
         <v>0</v>

--- a/grupos/3AEM - Estadisticos 20231.xlsx
+++ b/grupos/3AEM - Estadisticos 20231.xlsx
@@ -845,22 +845,22 @@
         <v>9</v>
       </c>
       <c r="T5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W5">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X5">
         <v>10</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -922,22 +922,22 @@
         <v>9</v>
       </c>
       <c r="T6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W6">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X6">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -999,22 +999,22 @@
         <v>10</v>
       </c>
       <c r="T7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X7">
         <v>10</v>
       </c>
       <c r="Y7">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1076,22 +1076,22 @@
         <v>10</v>
       </c>
       <c r="T8">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X8">
         <v>10</v>
       </c>
       <c r="Y8">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1153,22 +1153,22 @@
         <v>9</v>
       </c>
       <c r="T9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U9">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W9">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X9">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y9">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1230,22 +1230,22 @@
         <v>10</v>
       </c>
       <c r="T10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U10">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V10">
         <v>10</v>
       </c>
       <c r="W10">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X10">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1310,19 +1310,19 @@
         <v>5</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X11">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1384,16 +1384,16 @@
         <v>10</v>
       </c>
       <c r="T12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X12">
         <v>10</v>
@@ -1461,22 +1461,22 @@
         <v>8</v>
       </c>
       <c r="T13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V13">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W13">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="X13">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y13">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1538,19 +1538,19 @@
         <v>10</v>
       </c>
       <c r="T14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y14">
         <v>10</v>
@@ -1615,22 +1615,22 @@
         <v>7</v>
       </c>
       <c r="T15">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X15">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y15">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1692,22 +1692,22 @@
         <v>9</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1769,19 +1769,19 @@
         <v>10</v>
       </c>
       <c r="T17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y17">
         <v>10</v>
@@ -1846,22 +1846,22 @@
         <v>9</v>
       </c>
       <c r="T18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y18">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -1923,22 +1923,22 @@
         <v>8</v>
       </c>
       <c r="T19">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y19">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:25">
@@ -2003,7 +2003,7 @@
         <v>10</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V20">
         <v>10</v>
@@ -2077,22 +2077,22 @@
         <v>9</v>
       </c>
       <c r="T21">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W21">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X21">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="Y21">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2154,22 +2154,22 @@
         <v>10</v>
       </c>
       <c r="T22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W22">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X22">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y22">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2231,22 +2231,22 @@
         <v>10</v>
       </c>
       <c r="T23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="V23">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y23">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2308,19 +2308,19 @@
         <v>10</v>
       </c>
       <c r="T24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W24">
         <v>10</v>
       </c>
       <c r="X24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>10</v>
@@ -2388,19 +2388,19 @@
         <v>10</v>
       </c>
       <c r="U25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V25">
         <v>10</v>
       </c>
       <c r="W25">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X25">
         <v>10</v>
       </c>
       <c r="Y25">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2447,10 +2447,10 @@
         <v>5</v>
       </c>
       <c r="W26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="X26">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="Y26">
         <v>5</v>
@@ -2518,7 +2518,7 @@
         <v>10</v>
       </c>
       <c r="U27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V27">
         <v>10</v>
@@ -2595,13 +2595,13 @@
         <v>10</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W28">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X28">
         <v>10</v>
@@ -2669,22 +2669,22 @@
         <v>10</v>
       </c>
       <c r="T29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W29">
         <v>10</v>
       </c>
       <c r="X29">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="Y29">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2746,22 +2746,22 @@
         <v>8</v>
       </c>
       <c r="T30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="W30">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y30">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="31" spans="1:25">
@@ -2826,19 +2826,19 @@
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
       </c>
       <c r="X31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y31">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:25">
@@ -2909,10 +2909,10 @@
         <v>10</v>
       </c>
       <c r="W32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X32">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Y32">
         <v>10</v>
@@ -2977,22 +2977,22 @@
         <v>8</v>
       </c>
       <c r="T33">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="W33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X33">
         <v>10</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4932,7 +4932,7 @@
         <v>6.7</v>
       </c>
       <c r="H2">
-        <v>9.699999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I2">
         <v>0</v>
@@ -4964,7 +4964,7 @@
         <v>3.3</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="H4">
-        <v>10</v>
+        <v>7.4</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -5028,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -5060,7 +5060,7 @@
         <v>0</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -5092,7 +5092,7 @@
         <v>0</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I7">
         <v>0</v>
